--- a/out/Attention_Base_repeat_5_000001.xlsx
+++ b/out/Attention_Base_repeat_5_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC43" t="n">
-        <v>-1.265071245026775e-05</v>
+        <v>-3.823488901765086e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.005446922406043284</v>
+        <v>0.0164628331025979</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.01090859617873724</v>
+        <v>0.0329696011541154</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.02104516925453243</v>
+        <v>0.06360380332099881</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.04756572785386583</v>
+        <v>0.1437581307437981</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.006471507284415192</v>
+        <v>0.01956539545792371</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.03943903651123005</v>
+        <v>0.1192029444414931</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.001309207114581786</v>
+        <v>0.003967386336588986</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.03557825552718726</v>
+        <v>0.1075444986531238</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.001133345849728642</v>
+        <v>0.003435095476695675</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.03653416481421481</v>
+        <v>0.1104433786054307</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0005515140935196225</v>
+        <v>0.001676442581929727</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.03650267305885965</v>
+        <v>0.11035832090681</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0002602641296095585</v>
+        <v>0.0007974741049397474</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.03647176904999919</v>
+        <v>0.1102750209581912</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0001057853304050934</v>
+        <v>0.000329582832027443</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.03642210209622665</v>
+        <v>0.110135122268657</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>7.139547751258608e-05</v>
+        <v>0.0002265014470078366</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.03645977984416939</v>
+        <v>0.1102590118166688</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>2.721435118321863e-05</v>
+        <v>9.16430535496559e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.03644195751164819</v>
+        <v>0.1102154172815937</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>1.170429027768001e-05</v>
+        <v>4.511287083304001e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.1562253596518725</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.03643811816772702</v>
+        <v>0.1102139231631134</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>1.298369037402789e-06</v>
+        <v>1.494483528510883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.069469496003421</v>
+        <v>3.996122136721799</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.0364295164374439</v>
+        <v>0.1101979720362679</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>-1.564200431984666e-06</v>
+        <v>5.880031965381889e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.069469496003421</v>
+        <v>3.996122136721799</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.03642513046957273</v>
+        <v>0.1101947650205477</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-3.305984803435161e-06</v>
+        <v>8.204558969451803e-08</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.03642007084398786</v>
+        <v>0.110189602085982</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-3.934348768804317e-06</v>
+        <v>-2.335871922010791e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.03641494083104993</v>
+        <v>0.1101842770536372</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.538828146730642e-06</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.03640979619972408</v>
+        <v>0.1101789160511354</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.069469496003421</v>
+        <v>4.596122136721799</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.03640974837315734</v>
+        <v>0.1101737714772017</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1101685791914847</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.0364095172114179</v>
+        <v>0.110168443682879</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.03640955706689018</v>
+        <v>0.1101684835383513</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.03640959692236257</v>
+        <v>0.1101685233938235</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.03640958895126812</v>
+        <v>0.1101685154227291</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.03640974837315734</v>
+        <v>0.1101686748446182</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1101685791914847</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.03641000344818004</v>
+        <v>0.110168929919641</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.0364097563442518</v>
+        <v>0.1101686828157126</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.03640971648877941</v>
+        <v>0.1101686429602404</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1101685791914847</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.03640972445987386</v>
+        <v>0.1101686509313348</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1101685791914847</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.0364097563442518</v>
+        <v>0.1101686828157126</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.03640985199738526</v>
+        <v>0.1101687784688463</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.03640978822862962</v>
+        <v>0.1101687147000905</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.03640974837315734</v>
+        <v>0.1101686748446182</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.03640972445987386</v>
+        <v>0.1101686509313348</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.03640947735594562</v>
+        <v>0.1101684038274067</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.03640939764500107</v>
+        <v>0.1101683241164619</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.0364094454715678</v>
+        <v>0.1101683719430286</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.03640956503798475</v>
+        <v>0.1101684915094457</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.03640954909579572</v>
+        <v>0.1101684755672568</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.03640956503798475</v>
+        <v>0.1101684915094457</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.03640954909579572</v>
+        <v>0.1101684755672568</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.03640960489345703</v>
+        <v>0.110168531364918</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.03640960489345703</v>
+        <v>0.110168531364918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.03640960489345703</v>
+        <v>0.110168531364918</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.0364097563442518</v>
+        <v>0.1101686828157126</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.03640997156380222</v>
+        <v>0.1101688980352632</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.03640988388176309</v>
+        <v>0.1101688103532242</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.03640983605519636</v>
+        <v>0.1101687625266574</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.03640988388176309</v>
+        <v>0.1101688103532242</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.0364097005465905</v>
+        <v>0.1101686270180515</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.03640970851768495</v>
+        <v>0.1101686349891459</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.03640971648877941</v>
+        <v>0.1101686429602404</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.03640972445987386</v>
+        <v>0.1101686509313348</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.03640972445987386</v>
+        <v>0.1101686509313348</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.03640976431534625</v>
+        <v>0.1101686907868071</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.0364098280841019</v>
+        <v>0.110168754555563</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.03640993967942439</v>
+        <v>0.1101688661508854</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.03640998750599113</v>
+        <v>0.1101689139774521</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.03640994765051885</v>
+        <v>0.1101688741219798</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.03640987591066863</v>
+        <v>0.1101688023821297</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.03640999547708559</v>
+        <v>0.1101689219485465</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.03640983605519636</v>
+        <v>0.1101687625266574</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.03640960489345703</v>
+        <v>0.110168531364918</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.03640955706689018</v>
+        <v>0.1101684835383513</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.03640958895126812</v>
+        <v>0.1101685154227291</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1101685791914847</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1101685791914847</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.0364095730090792</v>
+        <v>0.1101684994805402</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.03640945344266226</v>
+        <v>0.1101683799141231</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.03640941358718998</v>
+        <v>0.1101683400586508</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.03640955706689018</v>
+        <v>0.1101684835383513</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.03640969257549604</v>
+        <v>0.110168619046957</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.03640967663330713</v>
+        <v>0.1101686031047681</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1101685791914847</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.03640961286455149</v>
+        <v>0.1101685393360124</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.03640950924032345</v>
+        <v>0.1101684357117845</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.03640938967390649</v>
+        <v>0.1101683161453675</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.03640950924032345</v>
+        <v>0.1101684357117845</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.03640955706689018</v>
+        <v>0.1101684835383513</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1101685791914847</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.03640953315360681</v>
+        <v>0.1101684596250679</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.7562253596518724</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.03640954112470127</v>
+        <v>0.1101684675961623</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_5_000001.xlsx
+++ b/out/Attention_Base_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.247209366080289</v>
+        <v>0.9485598254073502</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.247209366080289</v>
+        <v>0.9485598254073502</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.847209366080289</v>
+        <v>0.9485598254073502</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882167</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.847209366080289</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC43" t="n">
-        <v>-1.265071245026775e-05</v>
+        <v>-5.363801611273084e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.005446922406043284</v>
+        <v>0.02309486534135372</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.01090859617873724</v>
+        <v>0.04625157974308845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.02104516925453243</v>
+        <v>0.08922767860849957</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.04756572785386583</v>
+        <v>0.2016725738703844</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.006471507284415192</v>
+        <v>0.02744693412462048</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.03943903651123005</v>
+        <v>0.1672251711119893</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.001309207114581786</v>
+        <v>0.005568081507290677</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.03557825552718726</v>
+        <v>0.1508717544359197</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.001133345849728642</v>
+        <v>0.004820440897591852</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.03653416481421481</v>
+        <v>0.1549403457617648</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0005515140935196225</v>
+        <v>0.002354059742341042</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.03650267305885965</v>
+        <v>0.1548230314352403</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0002602641296095585</v>
+        <v>0.001120869164715632</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.03647176904999919</v>
+        <v>0.1547081896522397</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0001057853304050934</v>
+        <v>0.0004643067011632853</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.03642210209622665</v>
+        <v>0.1545139723556049</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>7.139547751258608e-05</v>
+        <v>0.0003198736973009973</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.03645977984416939</v>
+        <v>0.1546897605494296</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>2.721435118321863e-05</v>
+        <v>0.0001309445619931826</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.03644195751164819</v>
+        <v>0.1546306503061901</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>1.170429027768001e-05</v>
+        <v>6.515801916625601e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.03643811816772702</v>
+        <v>0.1546305489750044</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>1.298369037402789e-06</v>
+        <v>2.281779658186232e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.0364295164374439</v>
+        <v>0.1546102750349303</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>-1.564200431984666e-06</v>
+        <v>9.88846479473311e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.03642513046957273</v>
+        <v>0.1546077764189325</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-3.305984803435161e-06</v>
+        <v>2.340732518447637e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.03642007084398786</v>
+        <v>0.1546025446117132</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-3.934348768804317e-06</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.03641494083104993</v>
+        <v>0.1545970895664303</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.538828146730642e-06</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.03640979619972408</v>
+        <v>0.154591583932603</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.03640974837315734</v>
+        <v>0.1545863904378689</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1545811981521519</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.0364095172114179</v>
+        <v>0.1545810626435462</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.03640955706689018</v>
+        <v>0.1545811024990184</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.03640959692236257</v>
+        <v>0.1545811423544907</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.03640958895126812</v>
+        <v>0.1545811343833962</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.03640974837315734</v>
+        <v>0.1545812938052853</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1545811981521519</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.03641000344818004</v>
+        <v>0.1545815488803082</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.0364097563442518</v>
+        <v>0.1545813017763798</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.03640971648877941</v>
+        <v>0.1545812619209075</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1545811981521519</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.03640972445987386</v>
+        <v>0.154581269892002</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1545811981521519</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.0364097563442518</v>
+        <v>0.1545813017763798</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.03640985199738526</v>
+        <v>0.1545813974295135</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.03640978822862962</v>
+        <v>0.1545813336607576</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.03640974837315734</v>
+        <v>0.1545812938052853</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.03640972445987386</v>
+        <v>0.154581269892002</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.03640947735594562</v>
+        <v>0.1545810227880739</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.03640939764500107</v>
+        <v>0.1545809430771291</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.0364094454715678</v>
+        <v>0.1545809909036958</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.03640956503798475</v>
+        <v>0.1545811104701129</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.03640954909579572</v>
+        <v>0.154581094527924</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.03640956503798475</v>
+        <v>0.1545811104701129</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.03640954909579572</v>
+        <v>0.154581094527924</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.03640960489345703</v>
+        <v>0.1545811503255852</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.03640960489345703</v>
+        <v>0.1545811503255852</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.03640960489345703</v>
+        <v>0.1545811503255852</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.0364097563442518</v>
+        <v>0.1545813017763798</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.03640997156380222</v>
+        <v>0.1545815169959303</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.03640988388176309</v>
+        <v>0.1545814293138913</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.03640983605519636</v>
+        <v>0.1545813814873246</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.03640988388176309</v>
+        <v>0.1545814293138913</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.0364097005465905</v>
+        <v>0.1545812459787186</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.03640970851768495</v>
+        <v>0.1545812539498131</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.03640971648877941</v>
+        <v>0.1545812619209075</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.03640972445987386</v>
+        <v>0.154581269892002</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.03640972445987386</v>
+        <v>0.154581269892002</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.03640976431534625</v>
+        <v>0.1545813097474743</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.0364098280841019</v>
+        <v>0.1545813735162301</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.03640993967942439</v>
+        <v>0.1545814851115525</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.03640998750599113</v>
+        <v>0.1545815329381193</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.03640994765051885</v>
+        <v>0.154581493082647</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.03640987591066863</v>
+        <v>0.1545814213427969</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.03640999547708559</v>
+        <v>0.1545815409092137</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.03640983605519636</v>
+        <v>0.1545813814873246</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.03640960489345703</v>
+        <v>0.1545811503255852</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.03640955706689018</v>
+        <v>0.1545811024990184</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.03640958895126812</v>
+        <v>0.1545811343833962</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1545811981521519</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1545811981521519</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.0364095730090792</v>
+        <v>0.1545811184412073</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.03640945344266226</v>
+        <v>0.1545809988747903</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.03640941358718998</v>
+        <v>0.154580959019318</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.03640955706689018</v>
+        <v>0.1545811024990184</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.03640969257549604</v>
+        <v>0.1545812380076242</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.03640967663330713</v>
+        <v>0.1545812220654353</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1545811981521519</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.03640961286455149</v>
+        <v>0.1545811582966796</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.03640950924032345</v>
+        <v>0.1545810546724517</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.03640938967390649</v>
+        <v>0.1545809351060346</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.03640950924032345</v>
+        <v>0.1545810546724517</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.03640955706689018</v>
+        <v>0.1545811024990184</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.03640965272002376</v>
+        <v>0.1545811981521519</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.03640953315360681</v>
+        <v>0.1545810785857351</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.03640954112470127</v>
+        <v>0.1545810865568295</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_5_000001.xlsx
+++ b/out/Attention_Base_repeat_5_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.008639689534902573</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>1.563597470521927e-05</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.2999999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.00131554901599884</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.906657851026484</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.003264571540057659</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.906657851026484</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.003393633291125298</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.906657851026484</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.001144519075751305</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.906657851026484</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.00272050965577364</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.906657851026484</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.003882987424731255</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.906657851026484</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.003958022221922874</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.906657851026484</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.005198504775762558</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.706657851026484</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.005600530654191971</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.706657851026484</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.006342053413391113</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.706657851026484</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.006038718856871128</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.706657851026484</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.004900140687823296</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.003325514495372772</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001880611293017864</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001304764300584793</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0008498970419168472</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0004572533071041107</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.000634973868727684</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0008534640073776245</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0008041141554713249</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0004318663850426674</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.9485598254073502</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-8.262600749731064e-05</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0002546822652220726</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0002632075920701027</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0002280194312334061</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>7.462780922651291e-05</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9485598254073502</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0001057256013154984</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.9485598254073502</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0004795733839273453</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3904617997882167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0004764506593346596</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0005920371040701866</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0003771521151065826</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-8.207187056541443e-05</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1904617997882167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0002976451069116592</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.14855982540735</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0004876013845205307</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.906657851026484</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0005366392433643341</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.906657851026484</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0004496760666370392</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.148559825407351</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-9.979121387004852e-05</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3904617997882167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0009151967242360115</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.00226901937276125</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.003911979962140322</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-5.363801611273084e-05</v>
+        <v>-1.832464563928079e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.02309486534135372</v>
+        <v>0.007889953300800185</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.005018288269639015</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.04625157974308845</v>
+        <v>0.01580117777179286</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08922767860849957</v>
+        <v>0.03048388960583396</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.008016329258680344</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2016725738703844</v>
+        <v>0.06889896671024384</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.02744693412462048</v>
+        <v>0.00937620908896813</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01218671351671219</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1672251711119893</v>
+        <v>0.05712971148819337</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.005568081507290677</v>
+        <v>0.001898719333956945</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01399021781980991</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1508717544359197</v>
+        <v>0.05153961946045398</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.004820440897591852</v>
+        <v>0.001643811630141548</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01890746131539345</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1549403457617648</v>
+        <v>0.05292642706298525</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.002354059742341042</v>
+        <v>0.0008007204045799818</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01846479438245296</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1548230314352403</v>
+        <v>0.052883056390716</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001120869164715632</v>
+        <v>0.0003798668479977473</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.02019218727946281</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.1547081896522397</v>
+        <v>0.05284051900103851</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0004643067011632853</v>
+        <v>0.0001553325384757131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.02067289128899574</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.1545139723556049</v>
+        <v>0.05277087536944775</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0003198736973009973</v>
+        <v>0.0001061206945637616</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.02207156270742416</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1546897605494296</v>
+        <v>0.05282763904710929</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001309445619931826</v>
+        <v>4.138866570383483e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01984677091240883</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1546306503061901</v>
+        <v>0.05280417488827859</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>6.515801916625601e-05</v>
+        <v>1.905417799985921e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0200975090265274</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1546305489750044</v>
+        <v>0.05280084623303218</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>2.281779658186232e-05</v>
+        <v>4.447553556104185e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.02276093512773514</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1546102750349303</v>
+        <v>0.05279065885715792</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.88846479473311e-06</v>
+        <v>1.536993520230006e-07</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.02301246300339699</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1546077764189325</v>
+        <v>0.05278650816550106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.340732518447637e-06</v>
+        <v>-2.741313071246881e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.02432749047875404</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1546025446117132</v>
+        <v>0.05278143132175273</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-1.270220690815108e-06</v>
+        <v>-3.934348768804317e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.02311472594738007</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1545970895664303</v>
+        <v>0.05277626942443685</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-3.616484440191926e-06</v>
+        <v>-4.538828146730642e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.02236477844417095</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.154591583932603</v>
+        <v>0.05277105305326101</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.173194643232597e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0219089537858963</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1545863904378689</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02061058767139912</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1545811981521519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.02053641714155674</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1545810626435462</v>
+        <v>0.05276572514415463</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0200175903737545</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1545811024990184</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.02088915184140205</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1545811423544907</v>
+        <v>0.05276580485509918</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.02004840597510338</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1545811343833962</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.02082773670554161</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1545812938052853</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0196770541369915</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1545811981521519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02134875766932964</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1545815488803082</v>
+        <v>0.05276621138091665</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02144599333405495</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1545813017763798</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02095293253660202</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1545812619209075</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.02193149551749229</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1545811981521519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.02172068506479263</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.154581269892002</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0211644358932972</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1545811981521519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01778123714029789</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1545813017763798</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02087730169296265</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1545813974295135</v>
+        <v>0.05276605993012199</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02289420366287231</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1545813336607576</v>
+        <v>0.05276599616136612</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02330009825527668</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1545812938052853</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.02135524526238441</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.154581269892002</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02135716751217842</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1545810227880739</v>
+        <v>0.05276568528868235</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02159737423062325</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1545809430771291</v>
+        <v>0.05276560557773756</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.02145363576710224</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1545809909036958</v>
+        <v>0.05276565340430429</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.02178614400327206</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1545811104701129</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.02092712372541428</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.154581094527924</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0208234004676342</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1545811104701129</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.02052630111575127</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.154581094527924</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.02065375074744225</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1545811503255852</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.02099853381514549</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1545811503255852</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.0191669873893261</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1545811503255852</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02089505456387997</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1545813017763798</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01912225782871246</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1545815169959303</v>
+        <v>0.05276617949653883</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02120759151875973</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1545814293138913</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02092843502759933</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.16</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1545813814873246</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02009141258895397</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1545814293138913</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02041362226009369</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1545812459787186</v>
+        <v>0.05276590847932711</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02018293924629688</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1545812539498131</v>
+        <v>0.05276591645042156</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01964854449033737</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1545812619209075</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.02007178030908108</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.154581269892002</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01978633925318718</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.154581269892002</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01818479970097542</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1545813097474743</v>
+        <v>0.05276597224808275</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01895198225975037</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1545813735162301</v>
+        <v>0.05276603601683862</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01905003935098648</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1545814851115525</v>
+        <v>0.052766147612161</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01982202380895615</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1545815329381193</v>
+        <v>0.05276619543872774</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01903026551008224</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.154581493082647</v>
+        <v>0.05276615558325546</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01890296302735806</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1545814213427969</v>
+        <v>0.05276608384340536</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01876649260520935</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1545815409092137</v>
+        <v>0.05276620340982219</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01765749976038933</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1545813814873246</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01818244718015194</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1545811503255852</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01806410402059555</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1545811024990184</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01863092556595802</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1545811343833962</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01811625808477402</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1545811981521519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01835451647639275</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1545811981521519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01787074655294418</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1545811184412073</v>
+        <v>0.05276578094181581</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01715030334889889</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1545809988747903</v>
+        <v>0.05276566137539875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01722138002514839</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.154580959019318</v>
+        <v>0.05276562151992647</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01716624572873116</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1545811024990184</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.0175208505243063</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1545812380076242</v>
+        <v>0.05276590050823265</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.01762803271412849</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1545812220654353</v>
+        <v>0.05276588456604374</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01706588640809059</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1545811981521519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01666228286921978</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1545811582966796</v>
+        <v>0.05276582079728809</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01558994501829147</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1545810546724517</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.01523047685623169</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1545809351060346</v>
+        <v>0.0527655976066431</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01623782888054848</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1545810546724517</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01603830605745316</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1545811024990184</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01649149134755135</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1545811981521519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01599287986755371</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.09000000000000052</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1545810785857351</v>
+        <v>0.05276574108634353</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01529482938349247</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.3000000000000006</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1545810865568295</v>
+        <v>0.05276574905743799</v>
       </c>
     </row>
   </sheetData>
